--- a/feat/migration-contenu-fhir/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/feat/migration-contenu-fhir/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:43:27+00:00</t>
+    <t>2026-07-01T12:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/feat/migration-contenu-fhir/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:03:19+00:00</t>
+    <t>2026-07-03T07:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/feat/migration-contenu-fhir/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:33:59+00:00</t>
+    <t>2026-07-08T09:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/ValueSet-fr-vs-allergy-substance.xlsx
+++ b/feat/migration-contenu-fhir/ig/ValueSet-fr-vs-allergy-substance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T09:43:12+00:00</t>
+    <t>2026-07-08T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
